--- a/data/trans_camb/IP42B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 20,91</t>
+          <t>-12,33; 19,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 17,42</t>
+          <t>-13,31; 16,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 14,02</t>
+          <t>-7,18; 13,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 16,47</t>
+          <t>-7,36; 14,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 12,6</t>
+          <t>-7,31; 11,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 11,56</t>
+          <t>-6,87; 10,89</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,62; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,18; —</t>
+          <t>-94,76; 656,69</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 35,34</t>
+          <t>4,26; 35,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,2</t>
+          <t>0,0; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 18,5</t>
+          <t>-15,8; 16,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 11,76</t>
+          <t>-17,28; 11,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 19,63</t>
+          <t>-5,24; 17,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,4</t>
+          <t>-7,67; 9,38</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-81,17; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,81; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 8,03</t>
+          <t>-10,59; 7,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 7,75</t>
+          <t>-10,48; 7,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 22,91</t>
+          <t>1,03; 22,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 16,15</t>
+          <t>-2,03; 13,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 11,48</t>
+          <t>-1,82; 11,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 8,17</t>
+          <t>-3,2; 8,24</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 1041,95</t>
+          <t>-53,81; 857,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 22,63</t>
+          <t>2,21; 22,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 8,75</t>
+          <t>-5,73; 8,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 11,64</t>
+          <t>-4,34; 10,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 5,28</t>
+          <t>-7,48; 4,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,49</t>
+          <t>1,82; 14,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,71</t>
+          <t>-4,25; 4,94</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1150,78</t>
+          <t>3,09; 1293,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 550,0</t>
+          <t>-75,98; 593,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 535,72</t>
+          <t>-53,34; 472,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-83,87; 285,62</t>
+          <t>-80,11; 279,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,96; 400,77</t>
+          <t>17,45; 441,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 145,4</t>
+          <t>-57,17; 175,38</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 16,26</t>
+          <t>-24,06; 17,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 3,0</t>
+          <t>-34,51; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 24,38</t>
+          <t>-3,58; 25,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 3,96</t>
+          <t>-20,96; 4,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 16,72</t>
+          <t>-7,25; 15,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 0,67</t>
+          <t>-18,61; 1,67</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 277,06</t>
+          <t>-64,42; 326,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,97; 61,36</t>
+          <t>-89,94; 71,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 588,82</t>
+          <t>-31,42; 559,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-92,82; 144,8</t>
+          <t>-91,12; 168,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 221,61</t>
+          <t>-31,01; 197,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 15,41</t>
+          <t>-81,96; 32,09</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-50,65; 48,48</t>
+          <t>-52,41; 41,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-70,02; 18,26</t>
+          <t>-69,04; 13,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 38,17</t>
+          <t>-67,99; 34,73</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 41,5</t>
+          <t>-55,39; 36,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 25,69</t>
+          <t>-43,98; 25,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 13,14</t>
+          <t>-53,13; 9,54</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 301,79</t>
+          <t>-71,65; 223,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 129,28</t>
+          <t>-88,42; 90,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,1; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-79,12; —</t>
+          <t>-78,69; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 100,3</t>
+          <t>-62,91; 96,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 58,69</t>
+          <t>-76,25; 35,94</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,58</t>
+          <t>1,28; 13,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 3,77</t>
+          <t>-6,27; 4,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,62; 12,71</t>
+          <t>1,74; 13,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,99</t>
+          <t>-3,82; 4,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,49</t>
+          <t>3,39; 11,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,26</t>
+          <t>-3,38; 3,26</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,67; 247,9</t>
+          <t>10,31; 258,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 67,95</t>
+          <t>-53,5; 81,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,48; 298,06</t>
+          <t>14,56; 279,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 137,05</t>
+          <t>-43,21; 109,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>35,61; 206,76</t>
+          <t>33,72; 206,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 60,04</t>
+          <t>-35,76; 59,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 19,72</t>
+          <t>-12,1; 20,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 16,63</t>
+          <t>-13,52; 15,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 13,42</t>
+          <t>-7,14; 13,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 14,88</t>
+          <t>-7,18; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 11,84</t>
+          <t>-7,27; 13,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 10,89</t>
+          <t>-6,52; 11,91</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,76; 656,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 35,72</t>
+          <t>4,28; 35,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,48</t>
+          <t>0,0; 18,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 16,29</t>
+          <t>-18,83; 19,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 11,91</t>
+          <t>-22,68; 11,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 17,47</t>
+          <t>-4,35; 19,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 9,38</t>
+          <t>-7,52; 9,55</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,17; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 7,61</t>
+          <t>-9,72; 7,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 7,56</t>
+          <t>-10,57; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 22,73</t>
+          <t>0,97; 22,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 13,33</t>
+          <t>-1,93; 14,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 11,04</t>
+          <t>-1,03; 12,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 8,24</t>
+          <t>-3,43; 8,4</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 857,25</t>
+          <t>-46,57; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 22,33</t>
+          <t>2,55; 21,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 8,6</t>
+          <t>-5,3; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,93</t>
+          <t>-3,36; 11,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,78</t>
+          <t>-7,22; 5,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 14,05</t>
+          <t>1,4; 13,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,94</t>
+          <t>-4,45; 4,81</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 1293,87</t>
+          <t>-0,22; 1117,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 593,62</t>
+          <t>-71,19; 660,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 472,89</t>
+          <t>-50,33; 498,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,11; 279,11</t>
+          <t>-84,91; 281,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,45; 441,87</t>
+          <t>8,87; 466,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 175,38</t>
+          <t>-56,09; 181,68</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 17,21</t>
+          <t>-24,3; 16,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 3,15</t>
+          <t>-33,96; 3,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 25,97</t>
+          <t>-4,06; 24,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 4,17</t>
+          <t>-20,28; 5,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 15,94</t>
+          <t>-5,94; 17,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 1,67</t>
+          <t>-20,34; 0,76</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 326,24</t>
+          <t>-67,79; 320,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,94; 71,5</t>
+          <t>-89,35; 90,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 559,15</t>
+          <t>-28,24; 653,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-91,12; 168,87</t>
+          <t>-88,52; 272,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 197,02</t>
+          <t>-28,22; 236,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 32,09</t>
+          <t>-81,05; 23,13</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 41,2</t>
+          <t>-52,36; 36,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 13,64</t>
+          <t>-70,89; 10,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 34,73</t>
+          <t>-60,88; 38,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 36,07</t>
+          <t>-60,27; 47,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 25,96</t>
+          <t>-42,35; 26,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 9,54</t>
+          <t>-54,5; 11,89</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 223,69</t>
+          <t>-69,69; 168,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,42; 90,76</t>
+          <t>-88,63; 50,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,15; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-78,69; —</t>
+          <t>-80,38; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 96,92</t>
+          <t>-62,51; 108,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,25; 35,94</t>
+          <t>-75,39; 51,3</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,38</t>
+          <t>1,83; 13,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,16</t>
+          <t>-6,74; 3,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,04</t>
+          <t>1,64; 12,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,45</t>
+          <t>-3,28; 4,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,29</t>
+          <t>3,06; 11,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,26</t>
+          <t>-3,23; 3,3</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,31; 258,48</t>
+          <t>12,87; 251,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 81,8</t>
+          <t>-55,09; 60,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14,56; 279,21</t>
+          <t>16,22; 276,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 109,6</t>
+          <t>-39,44; 127,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>33,72; 206,82</t>
+          <t>30,02; 197,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 59,81</t>
+          <t>-35,15; 59,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>3,56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2,01</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 20,04</t>
+          <t>-7,18; 14,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 15,76</t>
+          <t>-7,12; 16,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 13,16</t>
+          <t>-11,85; 20,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 14,01</t>
+          <t>-13,05; 17,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 13,23</t>
+          <t>-6,61; 12,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 11,91</t>
+          <t>-7,14; 11,56</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>45,57%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>25,7%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,62; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,18; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,43</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>13,5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>5,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 35,46</t>
+          <t>-15,31; 18,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,27</t>
+          <t>-18,21; 11,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 19,51</t>
+          <t>4,22; 35,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 11,01</t>
+          <t>0,0; 17,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 19,09</t>
+          <t>-5,42; 19,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,55</t>
+          <t>-7,55; 9,4</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-14,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-14,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,81; —</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-1,84</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 7,78</t>
+          <t>2,05; 22,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 7,35</t>
+          <t>-1,77; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 22,32</t>
+          <t>-10,31; 8,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 14,24</t>
+          <t>-10,12; 7,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 12,43</t>
+          <t>-1,45; 11,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 8,4</t>
+          <t>-3,85; 8,17</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>498,82%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>223,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-36,45%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>498,82%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>223,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,57; —</t>
+          <t>-50,26; 1041,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>12,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,75</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 21,85</t>
+          <t>-3,2; 11,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,37</t>
+          <t>-7,84; 5,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 11,15</t>
+          <t>2,85; 22,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,47</t>
+          <t>-5,15; 8,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,79</t>
+          <t>1,36; 13,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,81</t>
+          <t>-5,14; 4,71</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>67,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-15,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>241,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>32,98%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>67,56%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-15,43%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1117,74</t>
+          <t>-49,79; 535,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 660,06</t>
+          <t>-83,87; 285,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 498,69</t>
+          <t>-2,45; 1150,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 281,54</t>
+          <t>-70,76; 550,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,87; 466,84</t>
+          <t>12,96; 400,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 181,68</t>
+          <t>-59,51; 145,4</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11,44</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-5,69</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-11,99</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>11,44</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-5,69</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 16,84</t>
+          <t>-5,22; 24,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 3,47</t>
+          <t>-21,63; 3,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 24,82</t>
+          <t>-23,51; 16,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 5,06</t>
+          <t>-34,12; 3,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 17,05</t>
+          <t>-7,16; 16,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 0,76</t>
+          <t>-20,03; 0,67</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-49,04%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-4,18%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-61,28%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-49,04%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 320,43</t>
+          <t>-37,04; 588,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 90,81</t>
+          <t>-92,82; 144,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 653,12</t>
+          <t>-65,49; 277,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-88,52; 272,7</t>
+          <t>-89,97; 61,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 236,69</t>
+          <t>-31,78; 221,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 23,13</t>
+          <t>-81,85; 15,41</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-9,27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-7,38</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-8,38</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-29,75</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-9,27</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-7,38</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 36,23</t>
+          <t>-62,49; 38,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-70,89; 10,82</t>
+          <t>-59,35; 41,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 38,66</t>
+          <t>-50,65; 48,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 47,03</t>
+          <t>-70,02; 18,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 26,8</t>
+          <t>-40,62; 25,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 11,89</t>
+          <t>-50,78; 13,14</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-21,94%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-17,48%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-15,3%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-54,36%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-21,94%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-17,48%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,69; 168,52</t>
+          <t>-83,1; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,63; 50,06</t>
+          <t>-79,12; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,15; —</t>
+          <t>-70,72; 301,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-80,38; —</t>
+          <t>-88,29; 129,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 108,46</t>
+          <t>-63,61; 100,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,39; 51,3</t>
+          <t>-72,86; 58,69</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>7,2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>7,45</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,66</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,83; 13,86</t>
+          <t>1,62; 12,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,6</t>
+          <t>-3,44; 4,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,34</t>
+          <t>1,35; 13,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,75</t>
+          <t>-6,04; 3,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,16</t>
+          <t>3,5; 11,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 3,3</t>
+          <t>-2,98; 3,26</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>110,59%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>89,58%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-7,94%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>110,59%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,87; 251,11</t>
+          <t>13,48; 298,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 60,65</t>
+          <t>-42,43; 137,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16,22; 276,5</t>
+          <t>8,67; 247,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 127,01</t>
+          <t>-52,27; 67,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,02; 197,5</t>
+          <t>35,61; 206,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 59,14</t>
+          <t>-31,88; 60,04</t>
         </is>
       </c>
     </row>
